--- a/Unified_PDF_Platform/unified_outputs/AMWINS Transamerica BLH Feb-25 Inv (1)_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/AMWINS Transamerica BLH Feb-25 Inv (1)_invoice.xlsx
@@ -534,26 +534,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MICHELLE M</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>MICHELLE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -595,17 +595,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -638,26 +634,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>THURMAN L</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>THURMAN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -699,17 +695,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>FF</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -751,17 +743,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -794,26 +782,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ELIZABETH A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>ELIZABETH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -846,26 +834,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALISHA N</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>ALISHA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -898,26 +886,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RYAN M</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>RYAN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -950,26 +938,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NATHAN J</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>NATHAN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1011,17 +999,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1063,17 +1047,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1115,17 +1095,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1167,17 +1143,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1219,17 +1191,13 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1271,17 +1239,13 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1323,17 +1287,13 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>EC</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1375,17 +1335,13 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1427,17 +1383,13 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1470,26 +1422,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>STEPHANIE L</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>STEPHANIE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Medical And/Or Rx Benefits</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
+          <t>TRANSAMERICA GAP INSURANCE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -1522,20 +1474,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NATALIE L</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>NATALIE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N21" t="n">
         <v>44.91</v>
       </c>
@@ -1574,12 +1530,12 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N22" t="n">
         <v>44.91</v>
       </c>
@@ -1618,12 +1574,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N23" t="n">
         <v>44.91</v>
       </c>
@@ -1662,12 +1618,12 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N24" t="n">
         <v>44.91</v>
       </c>
@@ -1706,12 +1662,12 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N25" t="n">
         <v>44.91</v>
       </c>
@@ -1742,20 +1698,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WILLIAM M</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N26" t="n">
         <v>44.91</v>
       </c>
@@ -1794,12 +1754,12 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>94.90000000000001</v>
       </c>
@@ -1830,20 +1790,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JOHN W</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>94.90000000000001</v>
       </c>
@@ -1882,12 +1846,12 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N29" t="n">
         <v>44.91</v>
       </c>
@@ -1926,12 +1890,12 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N30" t="n">
         <v>44.91</v>
       </c>
@@ -1962,20 +1926,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VICKI L</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>VICKI</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N31" t="n">
         <v>44.91</v>
       </c>
@@ -2006,20 +1974,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PATRICIA A</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>PATRICIA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N32" t="n">
         <v>44.91</v>
       </c>
@@ -2058,12 +2030,12 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N33" t="n">
         <v>44.91</v>
       </c>
@@ -2094,20 +2066,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DALTON J</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>DALTON</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>94.90000000000001</v>
       </c>
@@ -2146,12 +2122,12 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>94.90000000000001</v>
       </c>
@@ -2182,20 +2158,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JAMES C</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>136.92</v>
       </c>
@@ -2234,12 +2214,12 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N37" t="n">
         <v>44.91</v>
       </c>
@@ -2270,20 +2250,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HEATHER M</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>HEATHER</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>80.17</v>
       </c>
@@ -2321,17 +2305,23 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>TC3 CW 2000/2000 Plan (IP, OP, 2500AMB, INF, EC, ILAB)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N39" t="n">
         <v>44.91</v>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>44.91</v>
+      </c>
       <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2366,12 +2356,12 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N40" t="n">
         <v>44.91</v>
       </c>
@@ -2402,20 +2392,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ANDREA M</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>ANDREA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>44.91</v>
       </c>
@@ -2446,20 +2440,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BREE A</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>BREE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N42" t="n">
         <v>44.91</v>
       </c>
@@ -2490,20 +2488,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DAVID A</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>94.90000000000001</v>
       </c>
@@ -2534,20 +2536,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARY SAINT</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>MARY</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SAINT</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N44" t="n">
         <v>44.91</v>
       </c>
@@ -2586,12 +2592,12 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N45" t="n">
         <v>44.91</v>
       </c>
@@ -2622,20 +2628,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ERWIN M</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>ERWIN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N46" t="n">
         <v>44.91</v>
       </c>
@@ -2674,12 +2684,12 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N47" t="n">
         <v>44.91</v>
       </c>
@@ -2718,12 +2728,12 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N48" t="n">
         <v>44.91</v>
       </c>
@@ -2754,20 +2764,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BRIAN K</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>BRIAN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>136.92</v>
       </c>
@@ -2806,12 +2820,12 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
       <c r="N50" t="n">
         <v>44.91</v>
       </c>
@@ -2842,10 +2856,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>STEVEN A</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>STEVEN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -2863,47 +2881,23 @@
       <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AMWINS Transamerica BLH Feb-25 Inv (1).pdf</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>8789335</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>02/01/2025 - 02/28/2025</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SPAIN</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>NETRECIA</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>TC3 CW 2000/2000 Plan (IP, OP, 2500AMB, INF, EC, ILAB)</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>44.91</v>
-      </c>
+      <c r="N52" t="n">
+        <v>2797.09</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
     </row>
   </sheetData>
